--- a/data/export/2026-10-09-operations.xlsx
+++ b/data/export/2026-10-09-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,17 +704,17 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -720,13 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -792,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -831,7 +839,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -842,7 +850,7 @@
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -908,7 +916,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -947,7 +955,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -958,7 +966,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -991,32 +999,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1036,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,17 +1060,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1068,13 +1080,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1156,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1190,7 +1206,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1272,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1322,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1388,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1438,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1451,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1483,12 +1499,12 @@
       <c r="N9" s="2" t="inlineStr"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1518,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1554,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1615,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1634,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,77 +1670,73 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1738,7 +1750,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1748,17 +1760,17 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1768,45 +1780,41 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>152.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1839,12 +1847,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1858,7 +1866,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1894,35 +1902,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1955,12 +1963,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1974,7 +1982,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2010,35 +2018,35 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2071,12 +2079,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2090,7 +2098,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2115,7 +2123,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2126,35 +2134,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2187,12 +2195,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2206,7 +2214,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2231,7 +2239,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2242,7 +2250,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -2255,22 +2263,22 @@
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2308,7 +2316,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2322,7 +2330,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2358,7 +2366,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2379,7 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2381,7 +2389,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2391,40 +2399,44 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2438,7 +2450,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,17 +2460,17 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2468,83 +2480,83 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>152.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2558,7 +2570,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2568,17 +2580,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2588,45 +2600,41 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2659,12 +2667,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2678,7 +2686,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2714,35 +2722,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2775,12 +2783,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2794,7 +2802,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2830,35 +2838,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2891,12 +2899,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2910,7 +2918,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2946,7 +2954,3487 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-operations.xlsx
+++ b/data/export/2026-10-09-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD51"/>
+  <dimension ref="A1:AD80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,14 +719,14 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>70.0</t>
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       <c r="AC3" s="2" t="inlineStr"/>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       <c r="AC4" s="2" t="inlineStr"/>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1009,24 +1009,24 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1075,22 +1075,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1123,32 +1123,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1156,7 +1160,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1180,33 +1184,37 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1239,32 +1247,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1272,7 +1284,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1296,33 +1308,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1355,32 +1371,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1388,7 +1408,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1412,33 +1432,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1528,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1543,7 +1567,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -1554,7 +1578,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1644,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1670,7 +1694,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1703,32 +1727,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1736,7 +1764,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1760,33 +1788,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1884,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1902,7 +1934,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1968,7 +2000,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2018,7 +2050,7 @@
       <c r="AC13" s="2" t="inlineStr"/>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2116,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2134,7 +2166,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2147,22 +2179,22 @@
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2200,7 +2232,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2214,7 +2246,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2244,41 +2276,45 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2311,12 +2347,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2330,7 +2366,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2355,7 +2391,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2366,77 +2402,73 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2450,7 +2482,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2460,65 +2492,65 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>1/20</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2551,12 +2583,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2570,7 +2602,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2606,35 +2638,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2667,12 +2699,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2686,7 +2718,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2711,46 +2743,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2783,12 +2819,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2802,7 +2838,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2827,46 +2863,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2899,12 +2939,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2918,7 +2958,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2943,46 +2983,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3015,12 +3059,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3034,7 +3078,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3059,7 +3103,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3070,35 +3114,35 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3131,12 +3175,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3150,7 +3194,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3175,18 +3219,22 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -3199,60 +3247,64 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3266,7 +3318,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3276,33 +3328,37 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3315,60 +3371,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3382,7 +3442,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3392,33 +3452,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -3431,60 +3495,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3498,7 +3566,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3508,17 +3576,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3528,13 +3596,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>142.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3619,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3557,7 +3629,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3595,12 +3667,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3614,7 +3686,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3639,7 +3711,7 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
@@ -3650,7 +3722,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3663,32 +3735,32 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq37，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3711,12 +3783,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3724,13 +3796,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr"/>
-      <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr"/>
-      <c r="U28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3766,7 +3854,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3867,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3789,7 +3877,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3827,12 +3915,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3846,7 +3934,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3882,7 +3970,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3983,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3905,7 +3993,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3943,12 +4031,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3962,7 +4050,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3998,7 +4086,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4011,22 +4099,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4059,12 +4147,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4078,7 +4166,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4114,7 +4202,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4127,22 +4215,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4175,12 +4263,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4194,7 +4282,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4230,7 +4318,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4243,22 +4331,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4291,12 +4379,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4310,7 +4398,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4346,7 +4434,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4359,22 +4447,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4407,12 +4495,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4426,7 +4514,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4462,7 +4550,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4475,22 +4563,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4523,12 +4611,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4542,7 +4630,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4578,35 +4666,35 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4639,12 +4727,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4658,7 +4746,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4683,7 +4771,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4694,35 +4782,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4755,12 +4843,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4774,7 +4862,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4810,35 +4898,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4871,12 +4959,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4890,7 +4978,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4926,35 +5014,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4987,12 +5075,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5006,7 +5094,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5042,35 +5130,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5103,12 +5191,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5122,7 +5210,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5158,35 +5246,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5219,12 +5307,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5238,7 +5326,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5274,35 +5362,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5335,12 +5423,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5354,7 +5442,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5390,35 +5478,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5451,12 +5539,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5470,7 +5558,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5506,35 +5594,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5567,12 +5655,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5586,7 +5674,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5622,35 +5710,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5683,12 +5771,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5702,7 +5790,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5738,35 +5826,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5799,12 +5887,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5818,7 +5906,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5854,35 +5942,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5915,12 +6003,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5934,7 +6022,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5970,35 +6058,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6031,12 +6119,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6050,7 +6138,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6086,35 +6174,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6147,12 +6235,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6166,7 +6254,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6202,35 +6290,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6263,12 +6351,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6282,7 +6370,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6318,35 +6406,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6379,12 +6467,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6398,7 +6486,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6423,7 +6511,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6434,7 +6522,3415 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-operations.xlsx
+++ b/data/export/2026-10-09-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD80"/>
+  <dimension ref="A1:AD101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -839,18 +839,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -916,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -955,18 +959,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1160,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1284,7 +1292,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1408,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1495,32 +1503,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1528,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1552,17 +1564,17 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1572,13 +1584,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1611,32 +1627,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1644,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1668,33 +1688,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -1737,24 +1761,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1764,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1813,12 +1837,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1851,32 +1875,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -1884,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1908,33 +1936,37 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -1967,32 +1999,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2000,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2024,33 +2060,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2083,32 +2123,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2116,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2140,33 +2184,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2319,32 +2367,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2352,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2376,33 +2428,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2524,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2588,7 +2644,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2704,7 +2760,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2824,7 +2880,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2944,7 +3000,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3064,7 +3120,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3108,13 +3164,17 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
@@ -3127,22 +3187,22 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>09:25</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3180,7 +3240,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3194,7 +3254,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3229,82 +3289,78 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>5/13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3318,7 +3374,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3328,17 +3384,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3353,82 +3409,78 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3442,7 +3494,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3452,17 +3504,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3477,82 +3529,78 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3566,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3576,65 +3624,65 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3667,12 +3715,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3686,7 +3734,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3711,56 +3759,60 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq37，推进8站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3783,12 +3835,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3796,29 +3848,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>物理seq28（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3843,18 +3879,22 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3907,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3877,7 +3917,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3887,40 +3927,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3934,7 +3978,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3944,33 +3988,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3983,7 +4031,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3993,7 +4041,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4003,32 +4051,36 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4036,7 +4088,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4050,7 +4102,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4060,33 +4112,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4155,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4109,7 +4165,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4119,40 +4175,44 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4166,7 +4226,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4176,33 +4236,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4279,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4225,7 +4289,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4263,12 +4327,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4282,7 +4346,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4307,7 +4371,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4331,7 +4395,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4341,7 +4405,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4351,12 +4415,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -4379,12 +4443,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4392,13 +4456,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
-      <c r="U33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4423,7 +4503,7 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4447,60 +4527,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4514,7 +4598,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4524,33 +4608,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4563,7 +4651,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4573,7 +4661,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4611,12 +4699,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4630,7 +4718,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4655,7 +4743,7 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
@@ -4679,60 +4767,64 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4746,7 +4838,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4756,33 +4848,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4795,22 +4891,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4843,12 +4939,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4862,7 +4958,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4887,7 +4983,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4911,22 +5007,22 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4959,12 +5055,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4978,7 +5074,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5003,7 +5099,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -5027,7 +5123,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5037,7 +5133,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5075,12 +5171,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5094,7 +5190,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5143,32 +5239,32 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -5191,12 +5287,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5204,13 +5300,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5259,7 +5371,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5269,7 +5381,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5307,12 +5419,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5326,7 +5438,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5375,7 +5487,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5385,7 +5497,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5423,12 +5535,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5442,7 +5554,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5491,32 +5603,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq40，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5544,7 +5656,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5552,13 +5664,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5607,7 +5735,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5617,7 +5745,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5655,12 +5783,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5674,7 +5802,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5723,22 +5851,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5771,12 +5899,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5790,7 +5918,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5839,22 +5967,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5887,12 +6015,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5906,7 +6034,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5955,22 +6083,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6003,12 +6131,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6022,7 +6150,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6071,7 +6199,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6081,7 +6209,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6119,12 +6247,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6138,7 +6266,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6187,7 +6315,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6197,7 +6325,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6235,12 +6363,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6254,7 +6382,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6303,22 +6431,22 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6351,12 +6479,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6370,7 +6498,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6419,22 +6547,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6467,12 +6595,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6486,7 +6614,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6535,22 +6663,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6583,12 +6711,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6602,7 +6730,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6627,22 +6755,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>159.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6655,22 +6779,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6708,7 +6832,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6722,7 +6846,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6747,22 +6871,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6775,22 +6895,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6828,7 +6948,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6842,7 +6962,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6867,7 +6987,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -6885,28 +7005,28 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6939,12 +7059,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6958,7 +7078,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6983,7 +7103,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -6994,35 +7114,35 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7055,12 +7175,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7074,7 +7194,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7099,7 +7219,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7110,35 +7230,35 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7171,12 +7291,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7190,7 +7310,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7220,83 +7340,83 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7310,7 +7430,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7320,17 +7440,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7345,82 +7465,78 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7434,7 +7550,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7444,17 +7560,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7469,40 +7585,40 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7535,12 +7651,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7554,7 +7670,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7590,35 +7706,35 @@
       <c r="AC60" s="2" t="inlineStr"/>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7651,12 +7767,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7670,7 +7786,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7695,7 +7811,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7706,77 +7822,73 @@
       <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7790,7 +7902,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7800,17 +7912,17 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7825,40 +7937,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7891,12 +8003,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7910,7 +8022,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7935,7 +8047,7 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7946,35 +8058,35 @@
       <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8007,12 +8119,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8026,7 +8138,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8056,41 +8168,45 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8123,12 +8239,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8142,7 +8258,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8167,7 +8283,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8178,35 +8294,35 @@
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8239,12 +8355,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8258,7 +8374,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8283,7 +8399,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8294,7 +8410,7 @@
       <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8307,22 +8423,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8355,12 +8471,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8374,7 +8490,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8399,7 +8515,7 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8423,7 +8539,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8433,7 +8549,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8471,12 +8587,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8490,7 +8606,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8515,7 +8631,7 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8539,22 +8655,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>07:45</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8592,7 +8708,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8606,7 +8722,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8631,7 +8747,7 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
@@ -8655,52 +8771,56 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8708,7 +8828,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8722,7 +8842,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8732,33 +8852,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8771,7 +8895,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -8781,7 +8905,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -8791,40 +8915,44 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8838,7 +8966,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8848,17 +8976,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8868,13 +8996,17 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8887,7 +9019,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8897,7 +9029,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8907,40 +9039,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8954,7 +9090,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -8964,33 +9100,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9003,22 +9143,22 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>08:09</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -9051,12 +9191,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9070,7 +9210,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9119,52 +9259,56 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9172,7 +9316,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9186,7 +9330,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9196,17 +9340,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9221,12 +9365,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9239,60 +9383,64 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9306,7 +9454,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9316,33 +9464,37 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9355,60 +9507,64 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9422,7 +9578,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9432,17 +9588,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9457,12 +9613,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9475,60 +9631,64 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9542,7 +9702,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9552,17 +9712,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9572,13 +9732,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC77" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9591,60 +9755,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9658,7 +9826,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9668,17 +9836,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9688,13 +9856,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC78" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9707,60 +9879,64 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9774,7 +9950,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9784,17 +9960,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9814,7 +9990,7 @@
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9827,7 +10003,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9837,7 +10013,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9847,40 +10023,44 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9894,41 +10074,2541 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W80" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X80" s="2" t="inlineStr">
+      <c r="X93" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y80" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z80" s="2" t="inlineStr">
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
+      <c r="AA93" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC80" s="2" t="inlineStr"/>
-      <c r="AD80" s="2" t="inlineStr">
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr"/>
+      <c r="AD101" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-10-09-operations.xlsx
+++ b/data/export/2026-10-09-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD118"/>
+  <dimension ref="A1:AD125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1455,14 +1455,14 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1827,14 +1827,14 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3059,14 +3059,14 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,36 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3260,7 +3264,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3284,17 +3288,17 @@
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3304,17 +3308,17 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3388,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3423,14 +3427,14 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -3438,7 +3442,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3508,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3543,7 +3547,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3624,7 +3628,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3711,32 +3715,36 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3744,7 +3752,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3768,17 +3776,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3788,17 +3796,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>11/13</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3872,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3984,7 +3992,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4038,7 +4046,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4112,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4158,7 +4166,7 @@
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4232,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4278,7 +4286,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4352,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4398,7 +4406,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>5/13</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -4411,22 +4419,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4459,12 +4467,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4478,7 +4486,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4508,87 +4516,83 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4602,7 +4606,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4612,22 +4616,22 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
@@ -4637,82 +4641,78 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>11/13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4736,107 +4736,103 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4850,7 +4846,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4860,22 +4856,22 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4885,12 +4881,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -4903,52 +4899,56 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4980,17 +4980,17 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5000,13 +5000,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -5019,52 +5023,56 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>06:36</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5072,7 +5080,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5080,29 +5088,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>物理seq28（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>07:51</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5112,17 +5104,17 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5132,13 +5124,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5147,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5161,7 +5157,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5181,34 +5177,34 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5222,7 +5218,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5257,12 +5253,12 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5275,7 +5271,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5285,7 +5281,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5328,7 +5324,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5342,7 +5338,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5391,7 +5387,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5401,7 +5397,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5411,44 +5407,40 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq29推进至seq64，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5456,13 +5448,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5472,17 +5480,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5492,17 +5500,13 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5515,60 +5519,64 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5582,7 +5590,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5592,17 +5600,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5612,13 +5620,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5631,64 +5643,60 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5702,7 +5710,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5712,17 +5720,17 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5732,17 +5740,13 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC43" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -5755,24 +5759,24 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5785,12 +5789,12 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
@@ -5807,12 +5811,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5826,7 +5830,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5861,12 +5865,12 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5883,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5889,7 +5893,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5899,12 +5903,12 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -5927,12 +5931,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5940,29 +5944,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>物理seq24（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>08:24</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>08:32</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5987,7 +5975,7 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
@@ -6011,24 +5999,24 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6041,34 +6029,34 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6082,7 +6070,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6117,12 +6105,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6135,60 +6123,64 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6202,7 +6194,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6212,17 +6204,17 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6232,13 +6224,17 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6247,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6261,7 +6257,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6276,7 +6272,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq62，推进25站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -6299,12 +6295,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6314,27 +6310,27 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>物理seq23（站名待映射）</t>
+          <t>物理seq24（站名待映射）</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6383,7 +6379,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6393,7 +6389,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6403,35 +6399,39 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6450,7 +6450,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6460,17 +6460,17 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6480,13 +6480,17 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6503,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6509,7 +6513,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6519,44 +6523,40 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6570,7 +6570,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6580,17 +6580,17 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6600,17 +6600,13 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>153.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6619,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6633,7 +6629,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6643,12 +6639,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq62，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
@@ -6684,13 +6680,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="2" t="inlineStr"/>
-      <c r="T51" s="2" t="inlineStr"/>
-      <c r="U51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>08:54</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6715,7 +6727,7 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6739,22 +6751,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6787,12 +6799,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6806,7 +6818,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6855,7 +6867,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6865,7 +6877,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6875,40 +6887,44 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6922,7 +6938,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6932,33 +6948,37 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6991,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6981,7 +7001,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -7019,12 +7039,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7038,7 +7058,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -7063,7 +7083,7 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
@@ -7087,22 +7107,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -7135,12 +7155,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7154,7 +7174,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7179,7 +7199,7 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7203,7 +7223,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7213,7 +7233,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7251,12 +7271,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7270,7 +7290,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7295,7 +7315,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7319,7 +7339,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7329,7 +7349,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7367,12 +7387,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7386,7 +7406,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7411,7 +7431,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7435,22 +7455,22 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7488,7 +7508,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7502,7 +7522,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7551,60 +7571,64 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7618,7 +7642,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7628,17 +7652,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7648,13 +7672,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7667,22 +7695,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7715,12 +7743,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7734,7 +7762,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7783,22 +7811,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7831,12 +7859,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7850,7 +7878,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7899,22 +7927,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>08:52</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7952,7 +7980,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7966,7 +7994,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7991,22 +8019,18 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>156.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8019,22 +8043,22 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -8067,12 +8091,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8086,7 +8110,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8111,22 +8135,18 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr">
-        <is>
-          <t>135.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8159,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8149,7 +8169,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8187,12 +8207,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8206,7 +8226,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8231,22 +8251,18 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8275,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8269,7 +8285,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8312,7 +8328,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8326,7 +8342,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8356,13 +8372,17 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -8375,22 +8395,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8428,7 +8448,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8442,7 +8462,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8472,13 +8492,17 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8515,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8501,7 +8525,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8539,12 +8563,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8558,7 +8582,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8593,12 +8617,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8635,7 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -8621,7 +8645,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8664,7 +8688,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8678,7 +8702,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8727,22 +8751,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8775,12 +8799,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8794,7 +8818,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8824,17 +8848,13 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -8847,22 +8867,22 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8895,12 +8915,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8914,7 +8934,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8944,13 +8964,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>158.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8963,22 +8987,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -9011,12 +9035,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9030,7 +9054,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9060,17 +9084,13 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr">
-        <is>
-          <t>146.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -9083,22 +9103,22 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -9131,12 +9151,12 @@
       <c r="N72" s="2" t="inlineStr"/>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9150,7 +9170,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9185,12 +9205,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9223,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9213,7 +9233,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9251,12 +9271,12 @@
       <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9270,7 +9290,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9300,17 +9320,13 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>167.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9339,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9333,7 +9349,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9371,12 +9387,12 @@
       <c r="N74" s="2" t="inlineStr"/>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9390,7 +9406,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9420,13 +9436,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9459,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9449,7 +9469,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9487,12 +9507,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9506,7 +9526,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9536,13 +9556,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -9555,22 +9579,22 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -9622,7 +9646,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9657,12 +9681,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -9675,22 +9699,22 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9723,12 +9747,12 @@
       <c r="N77" s="2" t="inlineStr"/>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9742,7 +9766,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9791,22 +9815,22 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -9839,12 +9863,12 @@
       <c r="N78" s="2" t="inlineStr"/>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9858,7 +9882,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9901,28 +9925,28 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9955,12 +9979,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9974,7 +9998,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -10004,41 +10028,45 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -10071,12 +10099,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10090,7 +10118,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10115,7 +10143,7 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
@@ -10126,35 +10154,35 @@
       <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -10187,12 +10215,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10206,7 +10234,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10231,92 +10259,84 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC81" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10330,7 +10350,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10340,107 +10360,99 @@
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr"/>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10454,7 +10466,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10464,37 +10476,33 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC83" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10515,7 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -10517,7 +10525,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -10527,44 +10535,40 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10578,7 +10582,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10588,17 +10592,17 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10608,17 +10612,13 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC84" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10631,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10698,7 +10698,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10747,64 +10747,60 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>07:00</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10818,7 +10814,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10828,17 +10824,17 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10848,17 +10844,17 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -10871,24 +10867,24 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>07:10</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -10901,34 +10897,34 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10942,7 +10938,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10967,22 +10963,22 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB87" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10995,7 +10991,7 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -11005,7 +11001,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -11025,12 +11021,12 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
@@ -11047,12 +11043,12 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11066,7 +11062,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -11091,7 +11087,7 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
@@ -11101,12 +11097,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11119,7 +11115,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -11129,7 +11125,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -11149,12 +11145,12 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
@@ -11171,7 +11167,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11190,7 +11186,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11215,22 +11211,22 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11243,7 +11239,7 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -11253,7 +11249,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -11263,44 +11259,40 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N90" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11314,7 +11306,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11324,37 +11316,33 @@
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC90" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11355,7 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -11377,7 +11365,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11397,7 +11385,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -11419,12 +11407,12 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11438,7 +11426,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11463,22 +11451,22 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB91" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11491,7 +11479,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11501,7 +11489,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11521,12 +11509,12 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
@@ -11543,12 +11531,12 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11562,7 +11550,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11587,22 +11575,22 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB92" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11615,7 +11603,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11625,7 +11613,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11645,12 +11633,12 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
@@ -11667,12 +11655,12 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11686,7 +11674,7 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W93" s="2" t="inlineStr">
@@ -11711,22 +11699,22 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11727,7 @@
       <c r="B94" s="2" t="inlineStr"/>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -11749,7 +11737,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11769,12 +11757,12 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
@@ -11791,12 +11779,12 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -11810,7 +11798,7 @@
       <c r="U94" s="2" t="inlineStr"/>
       <c r="V94" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W94" s="2" t="inlineStr">
@@ -11835,7 +11823,7 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
@@ -11845,12 +11833,12 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11863,52 +11851,56 @@
       <c r="B95" s="2" t="inlineStr"/>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11916,7 +11908,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11930,7 +11922,7 @@
       <c r="U95" s="2" t="inlineStr"/>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
@@ -11940,33 +11932,37 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC95" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11979,24 +11975,24 @@
       <c r="B96" s="2" t="inlineStr"/>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12009,24 +12005,24 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -12036,7 +12032,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12050,7 +12046,7 @@
       <c r="U96" s="2" t="inlineStr"/>
       <c r="V96" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W96" s="2" t="inlineStr">
@@ -12075,22 +12071,22 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB96" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -12103,60 +12099,64 @@
       <c r="B97" s="2" t="inlineStr"/>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>08:09</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12170,7 +12170,7 @@
       <c r="U97" s="2" t="inlineStr"/>
       <c r="V97" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W97" s="2" t="inlineStr">
@@ -12180,33 +12180,37 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC97" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -12219,24 +12223,24 @@
       <c r="B98" s="2" t="inlineStr"/>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12249,12 +12253,12 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
@@ -12271,12 +12275,12 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12290,7 +12294,7 @@
       <c r="U98" s="2" t="inlineStr"/>
       <c r="V98" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W98" s="2" t="inlineStr">
@@ -12315,22 +12319,22 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12347,7 @@
       <c r="B99" s="2" t="inlineStr"/>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -12353,7 +12357,7 @@
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12363,32 +12367,36 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N99" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12396,7 +12404,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12410,7 +12418,7 @@
       <c r="U99" s="2" t="inlineStr"/>
       <c r="V99" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W99" s="2" t="inlineStr">
@@ -12420,22 +12428,22 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
@@ -12445,12 +12453,12 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12463,7 +12471,7 @@
       <c r="B100" s="2" t="inlineStr"/>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -12473,7 +12481,7 @@
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -12483,44 +12491,40 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12534,7 +12538,7 @@
       <c r="U100" s="2" t="inlineStr"/>
       <c r="V100" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="W100" s="2" t="inlineStr">
@@ -12544,37 +12548,33 @@
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12587,24 +12587,24 @@
       <c r="B101" s="2" t="inlineStr"/>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12617,34 +12617,34 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12658,7 +12658,7 @@
       <c r="U101" s="2" t="inlineStr"/>
       <c r="V101" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W101" s="2" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -12711,7 +12711,7 @@
       <c r="B102" s="2" t="inlineStr"/>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -12731,44 +12731,40 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N102" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -12782,7 +12778,7 @@
       <c r="U102" s="2" t="inlineStr"/>
       <c r="V102" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="W102" s="2" t="inlineStr">
@@ -12792,37 +12788,33 @@
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC102" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr"/>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -12835,7 +12827,7 @@
       <c r="B103" s="2" t="inlineStr"/>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -12845,7 +12837,7 @@
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -12865,12 +12857,12 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
@@ -12892,7 +12884,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -12906,7 +12898,7 @@
       <c r="U103" s="2" t="inlineStr"/>
       <c r="V103" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W103" s="2" t="inlineStr">
@@ -12941,12 +12933,12 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12959,22 +12951,22 @@
       <c r="B104" s="2" t="inlineStr"/>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>08:57</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
@@ -13012,7 +13004,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13026,7 +13018,7 @@
       <c r="U104" s="2" t="inlineStr"/>
       <c r="V104" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W104" s="2" t="inlineStr">
@@ -13056,13 +13048,17 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC104" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -13075,55 +13071,59 @@
       <c r="B105" s="2" t="inlineStr"/>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr"/>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N105" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -13142,7 +13142,7 @@
       <c r="U105" s="2" t="inlineStr"/>
       <c r="V105" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W105" s="2" t="inlineStr">
@@ -13152,22 +13152,22 @@
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
@@ -13177,12 +13177,12 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -13195,7 +13195,7 @@
       <c r="B106" s="2" t="inlineStr"/>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -13215,40 +13215,44 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13262,7 +13266,7 @@
       <c r="U106" s="2" t="inlineStr"/>
       <c r="V106" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="W106" s="2" t="inlineStr">
@@ -13272,22 +13276,22 @@
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
@@ -13297,12 +13301,12 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -13315,55 +13319,59 @@
       <c r="B107" s="2" t="inlineStr"/>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N107" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13382,7 +13390,7 @@
       <c r="U107" s="2" t="inlineStr"/>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
@@ -13392,17 +13400,17 @@
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA107" s="2" t="inlineStr">
@@ -13412,7 +13420,7 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
@@ -13422,7 +13430,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -13435,60 +13443,64 @@
       <c r="B108" s="2" t="inlineStr"/>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N108" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13502,7 +13514,7 @@
       <c r="U108" s="2" t="inlineStr"/>
       <c r="V108" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W108" s="2" t="inlineStr">
@@ -13512,17 +13524,17 @@
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA108" s="2" t="inlineStr">
@@ -13532,17 +13544,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -13555,22 +13567,22 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -13603,12 +13615,12 @@
       <c r="N109" s="2" t="inlineStr"/>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13622,7 +13634,7 @@
       <c r="U109" s="2" t="inlineStr"/>
       <c r="V109" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="W109" s="2" t="inlineStr">
@@ -13647,22 +13659,18 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC109" s="2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC109" s="2" t="inlineStr"/>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -13675,60 +13683,64 @@
       <c r="B110" s="2" t="inlineStr"/>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N110" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -13742,7 +13754,7 @@
       <c r="U110" s="2" t="inlineStr"/>
       <c r="V110" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W110" s="2" t="inlineStr">
@@ -13752,37 +13764,37 @@
       </c>
       <c r="X110" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y110" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z110" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA110" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB110" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -13795,7 +13807,7 @@
       <c r="B111" s="2" t="inlineStr"/>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -13805,7 +13817,7 @@
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -13843,12 +13855,12 @@
       <c r="N111" s="2" t="inlineStr"/>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -13862,7 +13874,7 @@
       <c r="U111" s="2" t="inlineStr"/>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
@@ -13897,12 +13909,12 @@
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13927,7 @@
       <c r="B112" s="2" t="inlineStr"/>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -13925,7 +13937,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -13963,12 +13975,12 @@
       <c r="N112" s="2" t="inlineStr"/>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -13982,7 +13994,7 @@
       <c r="U112" s="2" t="inlineStr"/>
       <c r="V112" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W112" s="2" t="inlineStr">
@@ -14007,18 +14019,22 @@
       </c>
       <c r="AA112" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC112" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC112" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14047,7 @@
       <c r="B113" s="2" t="inlineStr"/>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -14041,7 +14057,7 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -14079,12 +14095,12 @@
       <c r="N113" s="2" t="inlineStr"/>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14098,7 +14114,7 @@
       <c r="U113" s="2" t="inlineStr"/>
       <c r="V113" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W113" s="2" t="inlineStr">
@@ -14128,17 +14144,17 @@
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -14151,22 +14167,22 @@
       <c r="B114" s="2" t="inlineStr"/>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
@@ -14199,12 +14215,12 @@
       <c r="N114" s="2" t="inlineStr"/>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14218,7 +14234,7 @@
       <c r="U114" s="2" t="inlineStr"/>
       <c r="V114" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W114" s="2" t="inlineStr">
@@ -14243,7 +14259,7 @@
       </c>
       <c r="AA114" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB114" s="2" t="inlineStr">
@@ -14253,12 +14269,12 @@
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -14271,22 +14287,22 @@
       <c r="B115" s="2" t="inlineStr"/>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -14324,7 +14340,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14338,7 +14354,7 @@
       <c r="U115" s="2" t="inlineStr"/>
       <c r="V115" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W115" s="2" t="inlineStr">
@@ -14373,12 +14389,12 @@
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14407,7 @@
       <c r="B116" s="2" t="inlineStr"/>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -14401,7 +14417,7 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -14444,7 +14460,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14458,7 +14474,7 @@
       <c r="U116" s="2" t="inlineStr"/>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
@@ -14483,17 +14499,17 @@
       </c>
       <c r="AA116" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
@@ -14511,7 +14527,7 @@
       <c r="B117" s="2" t="inlineStr"/>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -14521,7 +14537,7 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -14559,12 +14575,12 @@
       <c r="N117" s="2" t="inlineStr"/>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14578,7 +14594,7 @@
       <c r="U117" s="2" t="inlineStr"/>
       <c r="V117" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W117" s="2" t="inlineStr">
@@ -14627,22 +14643,22 @@
       <c r="B118" s="2" t="inlineStr"/>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="F118" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -14675,12 +14691,12 @@
       <c r="N118" s="2" t="inlineStr"/>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -14694,47 +14710,883 @@
       <c r="U118" s="2" t="inlineStr"/>
       <c r="V118" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="W118" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X118" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y118" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z118" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA118" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB118" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC118" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD118" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr"/>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P119" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R119" s="2" t="inlineStr"/>
+      <c r="S119" s="2" t="inlineStr"/>
+      <c r="T119" s="2" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W119" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X119" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y119" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z119" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA119" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB119" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC119" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD119" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr"/>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P120" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R120" s="2" t="inlineStr"/>
+      <c r="S120" s="2" t="inlineStr"/>
+      <c r="T120" s="2" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W120" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X120" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y120" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z120" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA120" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB120" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC120" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD120" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr"/>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P121" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R121" s="2" t="inlineStr"/>
+      <c r="S121" s="2" t="inlineStr"/>
+      <c r="T121" s="2" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="W121" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X121" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y121" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z121" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA121" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB121" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC121" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD121" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr"/>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P122" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R122" s="2" t="inlineStr"/>
+      <c r="S122" s="2" t="inlineStr"/>
+      <c r="T122" s="2" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W122" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X122" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y122" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z122" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA122" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB122" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC122" s="2" t="inlineStr"/>
+      <c r="AD122" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr"/>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr"/>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P123" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr"/>
+      <c r="S123" s="2" t="inlineStr"/>
+      <c r="T123" s="2" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X123" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y123" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z123" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA123" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB123" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC123" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AD123" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="W118" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr"/>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P124" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R124" s="2" t="inlineStr"/>
+      <c r="S124" s="2" t="inlineStr"/>
+      <c r="T124" s="2" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X118" s="2" t="inlineStr">
+      <c r="X124" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y118" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z118" s="2" t="inlineStr">
+      <c r="Y124" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z124" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA118" s="2" t="inlineStr">
+      <c r="AA124" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB118" s="2" t="inlineStr">
+      <c r="AB124" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC118" s="2" t="inlineStr">
+      <c r="AC124" s="2" t="inlineStr">
         <is>
           <t>102.0</t>
         </is>
       </c>
-      <c r="AD118" s="2" t="inlineStr">
+      <c r="AD124" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr"/>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr"/>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P125" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R125" s="2" t="inlineStr"/>
+      <c r="S125" s="2" t="inlineStr"/>
+      <c r="T125" s="2" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="W125" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X125" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y125" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z125" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA125" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB125" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC125" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD125" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-09-operations.xlsx
+++ b/data/export/2026-10-09-operations.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -844,17 +844,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3556,17 +3556,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4920,17 +4920,17 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5044,17 +5044,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5912,17 +5912,17 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6780,12 +6780,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7276,17 +7276,17 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8140,17 +8140,17 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8388,17 +8388,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -8716,7 +8716,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9376,17 +9376,17 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -9758,7 +9758,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10120,17 +10120,17 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
@@ -10681,12 +10681,12 @@
       <c r="L83" s="2" t="inlineStr"/>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10783,32 +10783,36 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10816,7 +10820,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10840,17 +10844,17 @@
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10860,12 +10864,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
@@ -10903,32 +10907,36 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -10936,7 +10944,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10960,17 +10968,17 @@
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10980,17 +10988,17 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -11023,32 +11031,36 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11056,7 +11068,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -11080,17 +11092,17 @@
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -11100,17 +11112,17 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -11143,32 +11155,36 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11176,7 +11192,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11200,17 +11216,17 @@
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -11220,12 +11236,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
@@ -11296,7 +11312,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11416,7 +11432,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11460,17 +11476,17 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
@@ -11540,7 +11556,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11594,7 +11610,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -11718,7 +11734,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11842,7 +11858,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -11962,7 +11978,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12300,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12338,7 +12354,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12478,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12668,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12706,7 +12722,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -12776,7 +12792,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12820,17 +12836,17 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -12966,7 +12982,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -13036,7 +13052,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13080,17 +13096,17 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -13276,7 +13292,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13346,7 +13362,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -13412,7 +13428,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13456,12 +13472,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AD105" s="2" t="inlineStr">
@@ -13536,7 +13552,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13656,7 +13672,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13700,17 +13716,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -13896,7 +13912,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13940,17 +13956,17 @@
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -14016,7 +14032,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14070,7 +14086,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -14140,7 +14156,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14184,17 +14200,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14264,7 +14280,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14388,7 +14404,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14566,7 +14582,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -14636,7 +14652,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14680,17 +14696,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14900,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15062,7 +15078,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -15128,7 +15144,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15182,7 +15198,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -15306,7 +15322,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -15430,7 +15446,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15768,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15806,7 +15822,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -15926,7 +15942,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -16120,7 +16136,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16174,7 +16190,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -16244,7 +16260,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16288,17 +16304,17 @@
       </c>
       <c r="AB128" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -16368,7 +16384,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16412,17 +16428,17 @@
       </c>
       <c r="AB129" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -16616,7 +16632,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16660,12 +16676,12 @@
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
@@ -16740,7 +16756,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16864,7 +16880,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16908,17 +16924,17 @@
       </c>
       <c r="AB133" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -17112,7 +17128,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17156,17 +17172,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -17236,7 +17252,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17290,7 +17306,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -17360,7 +17376,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17484,7 +17500,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17732,7 +17748,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17910,7 +17926,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -18034,7 +18050,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -18282,7 +18298,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -18348,7 +18364,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18538,7 +18554,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -18732,7 +18748,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18786,7 +18802,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -18980,7 +18996,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19024,12 +19040,12 @@
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC150" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AD150" s="2" t="inlineStr">
@@ -19104,7 +19120,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19228,7 +19244,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19282,7 +19298,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -19530,7 +19546,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -19654,7 +19670,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -19778,7 +19794,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -19972,7 +19988,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20026,7 +20042,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -20150,7 +20166,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -20348,7 +20364,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20392,17 +20408,17 @@
       </c>
       <c r="AB161" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -20468,7 +20484,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20588,7 +20604,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20632,17 +20648,17 @@
       </c>
       <c r="AB163" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC163" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -20712,7 +20728,7 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q164" s="2" t="inlineStr">
@@ -20756,17 +20772,17 @@
       </c>
       <c r="AB164" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC164" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -20836,7 +20852,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q165" s="2" t="inlineStr">
@@ -20880,17 +20896,17 @@
       </c>
       <c r="AB165" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC165" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -20960,7 +20976,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21014,7 +21030,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21084,7 +21100,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21128,17 +21144,17 @@
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -21208,7 +21224,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21332,7 +21348,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21386,7 +21402,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -21456,7 +21472,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21580,7 +21596,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21634,7 +21650,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21774,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -21882,7 +21898,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -22006,7 +22022,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -22076,7 +22092,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22378,7 +22394,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22572,7 +22588,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22626,7 +22642,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -22746,7 +22762,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -22779,32 +22795,36 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N181" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -22812,7 +22832,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22836,17 +22856,17 @@
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA181" s="2" t="inlineStr">
@@ -22856,17 +22876,17 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -22936,7 +22956,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23023,32 +23043,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -23056,7 +23080,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23080,17 +23104,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23100,12 +23124,12 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
@@ -23143,32 +23167,36 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N184" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23176,7 +23204,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23200,17 +23228,17 @@
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA184" s="2" t="inlineStr">
@@ -23220,17 +23248,17 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -23263,32 +23291,36 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N185" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23296,7 +23328,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23320,17 +23352,17 @@
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA185" s="2" t="inlineStr">
@@ -23340,17 +23372,17 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -23383,12 +23415,12 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq29推进至seq58，推进29站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -23416,7 +23448,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23424,10 +23456,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R186" s="2" t="inlineStr"/>
-      <c r="S186" s="2" t="inlineStr"/>
-      <c r="T186" s="2" t="inlineStr"/>
-      <c r="U186" s="2" t="inlineStr"/>
+      <c r="R186" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="U186" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V186" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -23503,32 +23551,36 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N187" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -23536,7 +23588,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23560,17 +23612,17 @@
       </c>
       <c r="X187" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y187" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z187" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA187" s="2" t="inlineStr">
@@ -23580,17 +23632,17 @@
       </c>
       <c r="AB187" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -23623,32 +23675,36 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N188" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23656,7 +23712,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23680,17 +23736,17 @@
       </c>
       <c r="X188" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y188" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z188" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA188" s="2" t="inlineStr">
@@ -23700,17 +23756,17 @@
       </c>
       <c r="AB188" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC188" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>141.8</t>
         </is>
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -23776,7 +23832,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23830,7 +23886,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -23863,12 +23919,12 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq52，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
@@ -23896,7 +23952,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23904,10 +23960,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R190" s="2" t="inlineStr"/>
-      <c r="S190" s="2" t="inlineStr"/>
-      <c r="T190" s="2" t="inlineStr"/>
-      <c r="U190" s="2" t="inlineStr"/>
+      <c r="R190" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S190" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="T190" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="U190" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V190" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24016,7 +24088,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24070,7 +24142,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -24103,32 +24175,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -24136,7 +24212,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24160,17 +24236,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24180,17 +24256,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -24256,7 +24332,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24310,7 +24386,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -24376,7 +24452,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24430,7 +24506,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -24496,7 +24572,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24616,7 +24692,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24660,17 +24736,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -24736,7 +24812,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24780,17 +24856,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -25224,7 +25300,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25278,7 +25354,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -25348,7 +25424,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25646,7 +25722,7 @@
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25792,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25765,12 +25841,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -25840,7 +25916,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25884,12 +25960,12 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
@@ -26266,7 +26342,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -26390,7 +26466,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -26514,7 +26590,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26584,7 +26660,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26628,17 +26704,17 @@
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26704,7 +26780,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26748,17 +26824,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -26882,7 +26958,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -27192,7 +27268,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27246,7 +27322,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -27370,7 +27446,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -27564,7 +27640,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27742,7 +27818,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -27932,7 +28008,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -27976,12 +28052,12 @@
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
@@ -28052,7 +28128,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28101,12 +28177,12 @@
       </c>
       <c r="AC224" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -28226,7 +28302,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -28474,7 +28550,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28668,7 +28744,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28712,17 +28788,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -29036,7 +29112,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q232" s="2" t="inlineStr">
@@ -29102,7 +29178,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -29350,7 +29426,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -29540,7 +29616,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29596,12 +29672,12 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
@@ -29730,7 +29806,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29930,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -30598,7 +30674,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -30846,7 +30922,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -31094,7 +31170,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -31660,7 +31736,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31704,17 +31780,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -31838,7 +31914,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -32086,7 +32162,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -32156,7 +32232,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32205,12 +32281,12 @@
       </c>
       <c r="AC257" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -32458,7 +32534,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -32528,7 +32604,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32706,7 +32782,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32826,7 +32902,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -33020,7 +33096,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33074,7 +33150,7 @@
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -33144,7 +33220,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33188,17 +33264,17 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -33392,7 +33468,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33436,12 +33512,12 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
@@ -33818,7 +33894,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -33888,7 +33964,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -33932,17 +34008,17 @@
       </c>
       <c r="AB271" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC271" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -34190,7 +34266,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -34314,7 +34390,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -34384,7 +34460,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34433,12 +34509,12 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -34686,7 +34762,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34756,7 +34832,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34934,7 +35010,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -35124,7 +35200,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35178,7 +35254,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -35248,7 +35324,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35292,17 +35368,17 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -35620,7 +35696,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35664,12 +35740,12 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35798,7 +35874,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -36042,7 +36118,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36112,7 +36188,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36156,17 +36232,17 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -36286,7 +36362,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -36352,7 +36428,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q291" s="2" t="inlineStr">
@@ -36401,12 +36477,12 @@
       </c>
       <c r="AC291" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -36530,7 +36606,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36724,7 +36800,7 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q294" s="2" t="inlineStr">
@@ -36833,12 +36909,12 @@
       <c r="L295" s="2" t="inlineStr"/>
       <c r="M295" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N295" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O295" s="2" t="inlineStr">
@@ -36848,7 +36924,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q295" s="2" t="inlineStr">
@@ -36902,7 +36978,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36945,24 +37021,24 @@
       </c>
       <c r="I296" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr"/>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N296" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O296" s="2" t="inlineStr">
@@ -36972,7 +37048,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37021,12 +37097,12 @@
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37059,32 +37135,36 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr"/>
       <c r="M297" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N297" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O297" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37092,7 +37172,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37116,17 +37196,17 @@
       </c>
       <c r="X297" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y297" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z297" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA297" s="2" t="inlineStr">
@@ -37136,12 +37216,12 @@
       </c>
       <c r="AB297" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
@@ -37179,32 +37259,36 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr"/>
       <c r="M298" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N298" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O298" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -37212,7 +37296,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37236,17 +37320,17 @@
       </c>
       <c r="X298" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y298" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z298" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA298" s="2" t="inlineStr">
@@ -37256,17 +37340,17 @@
       </c>
       <c r="AB298" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37299,32 +37383,36 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N299" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O299" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -37332,7 +37420,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37356,17 +37444,17 @@
       </c>
       <c r="X299" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y299" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z299" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA299" s="2" t="inlineStr">
@@ -37376,17 +37464,17 @@
       </c>
       <c r="AB299" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37452,7 +37540,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37501,12 +37589,12 @@
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37572,7 +37660,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37692,7 +37780,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37736,17 +37824,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
